--- a/data/operations.xlsx
+++ b/data/operations.xlsx
@@ -507,6 +507,7 @@
       <c r="H2" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="I2" s="0"/>
       <c r="J2" s="3" t="s">
         <v>20</v>
       </c>
@@ -551,6 +552,7 @@
       <c r="H3" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="I3" s="0"/>
       <c r="J3" s="3" t="s">
         <v>20</v>
       </c>
@@ -595,6 +597,7 @@
       <c r="H4" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="I4" s="0"/>
       <c r="J4" s="3" t="s">
         <v>20</v>
       </c>
@@ -639,6 +642,7 @@
       <c r="H5" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="I5" s="0"/>
       <c r="J5" s="3" t="s">
         <v>20</v>
       </c>
@@ -683,6 +687,7 @@
       <c r="H6" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="I6" s="0"/>
       <c r="J6" s="3" t="s">
         <v>28</v>
       </c>
@@ -724,6 +729,7 @@
       <c r="H7" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="I7" s="0"/>
       <c r="J7" s="3" t="s">
         <v>31</v>
       </c>
@@ -762,6 +768,7 @@
       <c r="H8" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="I8" s="0"/>
       <c r="J8" s="3" t="s">
         <v>31</v>
       </c>
@@ -803,6 +810,7 @@
       <c r="H9" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="I9" s="0"/>
       <c r="J9" s="3" t="s">
         <v>35</v>
       </c>
@@ -847,6 +855,9 @@
       <c r="H10" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="I10" s="5" t="n">
+        <v>12</v>
+      </c>
       <c r="J10" s="3" t="s">
         <v>35</v>
       </c>
@@ -891,6 +902,9 @@
       <c r="H11" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="I11" s="5" t="n">
+        <v>19</v>
+      </c>
       <c r="J11" s="3" t="s">
         <v>41</v>
       </c>
@@ -932,6 +946,9 @@
       <c r="H12" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="I12" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="J12" s="3" t="s">
         <v>41</v>
       </c>
@@ -973,6 +990,9 @@
       <c r="H13" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="I13" s="5" t="n">
+        <v>11</v>
+      </c>
       <c r="J13" s="3" t="s">
         <v>45</v>
       </c>
@@ -1111,7 +1131,6 @@
       <c r="H16" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I16" s="0"/>
       <c r="J16" s="3" t="s">
         <v>53</v>
       </c>
@@ -1156,7 +1175,6 @@
       <c r="H17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I17" s="0"/>
       <c r="J17" s="3" t="s">
         <v>53</v>
       </c>
@@ -1201,7 +1219,6 @@
       <c r="H18" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I18" s="0"/>
       <c r="J18" s="3" t="s">
         <v>48</v>
       </c>
@@ -1246,7 +1263,6 @@
       <c r="H19" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I19" s="0"/>
       <c r="J19" s="3" t="s">
         <v>60</v>
       </c>
@@ -1291,7 +1307,6 @@
       <c r="H20" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I20" s="0"/>
       <c r="J20" s="3" t="s">
         <v>60</v>
       </c>
@@ -1336,7 +1351,9 @@
       <c r="H21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I21" s="0"/>
+      <c r="I21" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="J21" s="3" t="s">
         <v>31</v>
       </c>
@@ -1381,7 +1398,9 @@
       <c r="H22" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="0"/>
+      <c r="I22" s="5" t="n">
+        <v>18</v>
+      </c>
       <c r="J22" s="3" t="s">
         <v>20</v>
       </c>
@@ -1426,7 +1445,9 @@
       <c r="H23" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I23" s="0"/>
+      <c r="I23" s="5" t="n">
+        <v>28</v>
+      </c>
       <c r="J23" s="3" t="s">
         <v>71</v>
       </c>
@@ -1471,7 +1492,9 @@
       <c r="H24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I24" s="0"/>
+      <c r="I24" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="J24" s="3" t="s">
         <v>71</v>
       </c>
@@ -1516,7 +1539,9 @@
       <c r="H25" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I25" s="0"/>
+      <c r="I25" s="5" t="n">
+        <v>7</v>
+      </c>
       <c r="J25" s="3" t="s">
         <v>28</v>
       </c>
@@ -1561,7 +1586,6 @@
       <c r="H26" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I26" s="0"/>
       <c r="J26" s="3" t="s">
         <v>60</v>
       </c>
@@ -1606,7 +1630,6 @@
       <c r="H27" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I27" s="0"/>
       <c r="J27" s="3" t="s">
         <v>28</v>
       </c>
@@ -1651,7 +1674,6 @@
       <c r="H28" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I28" s="0"/>
       <c r="J28" s="3" t="s">
         <v>20</v>
       </c>
@@ -1678,7 +1700,6 @@
       <c r="B29" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C29" s="0"/>
       <c r="D29" s="3" t="s">
         <v>18</v>
       </c>
@@ -1694,11 +1715,9 @@
       <c r="H29" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I29" s="0"/>
       <c r="J29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="K29" s="0"/>
       <c r="L29" s="3" t="s">
         <v>83</v>
       </c>
@@ -1719,7 +1738,6 @@
       <c r="B30" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C30" s="0"/>
       <c r="D30" s="3" t="s">
         <v>18</v>
       </c>
@@ -1735,11 +1753,9 @@
       <c r="H30" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I30" s="0"/>
       <c r="J30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="K30" s="0"/>
       <c r="L30" s="3" t="s">
         <v>83</v>
       </c>
@@ -1778,11 +1794,9 @@
       <c r="H31" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I31" s="0"/>
       <c r="J31" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="K31" s="0"/>
       <c r="L31" s="3" t="s">
         <v>86</v>
       </c>
